--- a/sample_data/KE/orders_2025-10.xlsx
+++ b/sample_data/KE/orders_2025-10.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M399"/>
+  <dimension ref="A1:M400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7719,9 +7719,6 @@
           <t>ks</t>
         </is>
       </c>
-      <c r="K143" t="n">
-        <v>6.39</v>
-      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -9450,11 +9447,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KE-000034</t>
+          <t>KE-000033</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -9471,16 +9468,16 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>C00191</t>
+          <t>C00138</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>BRK-C40-3P</t>
+          <t>WD-ELG-SOC2-AN</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -9488,7 +9485,7 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>17.8</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -9496,7 +9493,7 @@
         </is>
       </c>
       <c r="M177" t="n">
-        <v>356</v>
+        <v>1139.19</v>
       </c>
     </row>
     <row r="178">
@@ -9506,7 +9503,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -9528,11 +9525,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>WD-CLS-FR1-AN</t>
+          <t>BRK-C40-3P</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -9540,7 +9537,7 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>1.07</v>
+        <v>17.8</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9548,17 +9545,17 @@
         </is>
       </c>
       <c r="M178" t="n">
-        <v>2.14</v>
+        <v>356</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KE-000035</t>
+          <t>KE-000034</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -9575,16 +9572,16 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>C00140</t>
+          <t>C00191</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>WD-ELG-SW1-AN</t>
+          <t>WD-CLS-FR1-AN</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -9592,7 +9589,7 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>5.04</v>
+        <v>1.07</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9600,13 +9597,13 @@
         </is>
       </c>
       <c r="M179" t="n">
-        <v>5.04</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KE-000036</t>
+          <t>KE-000035</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -9627,16 +9624,16 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C00400</t>
+          <t>C00140</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>BRK-B40-3P</t>
+          <t>WD-ELG-SW1-AN</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -9644,7 +9641,7 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>19.23</v>
+        <v>5.04</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9652,7 +9649,7 @@
         </is>
       </c>
       <c r="M180" t="n">
-        <v>269.22</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="181">
@@ -9662,7 +9659,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -9684,11 +9681,11 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>BRK-B40-3P</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -9696,7 +9693,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>6.99</v>
+        <v>19.23</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9704,7 +9701,7 @@
         </is>
       </c>
       <c r="M181" t="n">
-        <v>118.83</v>
+        <v>269.22</v>
       </c>
     </row>
     <row r="182">
@@ -9714,7 +9711,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -9736,11 +9733,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>WD-NOV-FR1-WH</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -9748,7 +9745,7 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>1.49</v>
+        <v>6.99</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9756,7 +9753,7 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>20.86</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="183">
@@ -9766,7 +9763,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -9788,7 +9785,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-FR1-WH</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -9800,7 +9797,7 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>5.67</v>
+        <v>1.49</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9808,17 +9805,17 @@
         </is>
       </c>
       <c r="M183" t="n">
-        <v>79.38</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KE-000037</t>
+          <t>KE-000036</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -9835,16 +9832,16 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C00166</t>
+          <t>C00400</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>BRK-C20-3P</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -9852,7 +9849,7 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>18.81</v>
+        <v>5.67</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -9860,7 +9857,7 @@
         </is>
       </c>
       <c r="M184" t="n">
-        <v>244.53</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="185">
@@ -9870,7 +9867,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -9892,11 +9889,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>WD-CLS-SW6-WH</t>
+          <t>BRK-C20-3P</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -9904,7 +9901,7 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>3.35</v>
+        <v>18.81</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -9912,7 +9909,7 @@
         </is>
       </c>
       <c r="M185" t="n">
-        <v>30.15</v>
+        <v>244.53</v>
       </c>
     </row>
     <row r="186">
@@ -9922,7 +9919,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -9944,11 +9941,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-CLS-SW6-WH</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -9956,7 +9953,7 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>7.26</v>
+        <v>3.35</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -9964,7 +9961,7 @@
         </is>
       </c>
       <c r="M186" t="n">
-        <v>21.78</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="187">
@@ -9974,7 +9971,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -9996,11 +9993,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>WD-NOV-FR2-IV</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -10008,7 +10005,7 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>2.54</v>
+        <v>7.26</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10016,7 +10013,7 @@
         </is>
       </c>
       <c r="M187" t="n">
-        <v>22.86</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="188">
@@ -10026,7 +10023,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -10048,11 +10045,11 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-FR2-IV</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -10060,7 +10057,7 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>5.89</v>
+        <v>2.54</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10068,17 +10065,17 @@
         </is>
       </c>
       <c r="M188" t="n">
-        <v>94.23999999999999</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KE-000038</t>
+          <t>KE-000037</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -10095,24 +10092,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>C00202</t>
+          <t>C00166</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>CAB-CYA-4-BK</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K189" t="n">
-        <v>0.55</v>
+        <v>5.89</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10120,7 +10117,7 @@
         </is>
       </c>
       <c r="M189" t="n">
-        <v>148.5</v>
+        <v>94.23999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -10130,7 +10127,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -10152,19 +10149,19 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>WD-CLS-FR1-WH</t>
+          <t>CAB-CYA-4-BK</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K190" t="n">
-        <v>1.24</v>
+        <v>0.55</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10172,7 +10169,7 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>18.6</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="191">
@@ -10182,7 +10179,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -10204,11 +10201,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-IV</t>
+          <t>WD-CLS-FR1-WH</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -10216,7 +10213,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>4.01</v>
+        <v>1.24</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10224,7 +10221,7 @@
         </is>
       </c>
       <c r="M191" t="n">
-        <v>24.06</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="192">
@@ -10234,7 +10231,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -10256,11 +10253,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW1-IV</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -10268,7 +10265,7 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>7.1</v>
+        <v>4.01</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10276,7 +10273,7 @@
         </is>
       </c>
       <c r="M192" t="n">
-        <v>49.7</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="193">
@@ -10286,7 +10283,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -10308,11 +10305,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -10320,7 +10317,7 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>5.76</v>
+        <v>7.1</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10328,17 +10325,17 @@
         </is>
       </c>
       <c r="M193" t="n">
-        <v>103.68</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>KE-000039</t>
+          <t>KE-000038</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -10355,24 +10352,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C00275</t>
+          <t>C00202</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K194" t="n">
-        <v>2.16</v>
+        <v>5.76</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10380,7 +10377,7 @@
         </is>
       </c>
       <c r="M194" t="n">
-        <v>410.4</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="195">
@@ -10390,7 +10387,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -10412,19 +10409,19 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>BRK-C20-1P</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K195" t="n">
-        <v>4.91</v>
+        <v>2.16</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10432,7 +10429,7 @@
         </is>
       </c>
       <c r="M195" t="n">
-        <v>49.1</v>
+        <v>410.4</v>
       </c>
     </row>
     <row r="196">
@@ -10442,7 +10439,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -10464,11 +10461,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>BRK-C40-1P</t>
+          <t>BRK-C20-1P</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -10476,7 +10473,7 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>5.56</v>
+        <v>4.91</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -10484,7 +10481,7 @@
         </is>
       </c>
       <c r="M196" t="n">
-        <v>22.24</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="197">
@@ -10494,7 +10491,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -10516,11 +10513,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>RCD-40-30-2P</t>
+          <t>BRK-C40-1P</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -10528,7 +10525,7 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>24.92</v>
+        <v>5.56</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -10536,7 +10533,7 @@
         </is>
       </c>
       <c r="M197" t="n">
-        <v>498.4</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="198">
@@ -10546,7 +10543,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -10568,11 +10565,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>RCD-40-30-2P</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -10580,7 +10577,7 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>6.99</v>
+        <v>24.92</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -10588,17 +10585,17 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>34.95</v>
+        <v>498.4</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>KE-000040</t>
+          <t>KE-000039</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -10615,24 +10612,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00275</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BK</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1030</v>
+        <v>5</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K199" t="n">
-        <v>0.92</v>
+        <v>6.99</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -10640,7 +10637,7 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>947.6</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="200">
@@ -10650,7 +10647,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -10672,19 +10669,19 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>BRK-C16-1P</t>
+          <t>CAB-CYA-6-BK</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>169</v>
+        <v>1030</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K200" t="n">
-        <v>3.66</v>
+        <v>0.92</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -10692,7 +10689,7 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>618.54</v>
+        <v>947.6</v>
       </c>
     </row>
     <row r="201">
@@ -10702,7 +10699,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -10724,11 +10721,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>RCBO-B16-30</t>
+          <t>BRK-C16-1P</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -10736,7 +10733,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>25.35</v>
+        <v>3.66</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -10744,7 +10741,7 @@
         </is>
       </c>
       <c r="M201" t="n">
-        <v>3396.9</v>
+        <v>618.54</v>
       </c>
     </row>
     <row r="202">
@@ -10754,7 +10751,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -10776,11 +10773,11 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>WD-CLS-SW5-WH</t>
+          <t>RCBO-B16-30</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -10788,7 +10785,7 @@
         </is>
       </c>
       <c r="K202" t="n">
-        <v>3.14</v>
+        <v>25.35</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -10796,7 +10793,7 @@
         </is>
       </c>
       <c r="M202" t="n">
-        <v>474.14</v>
+        <v>3396.9</v>
       </c>
     </row>
     <row r="203">
@@ -10806,7 +10803,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -10828,11 +10825,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>LED-PNL-60x60-40W</t>
+          <t>WD-CLS-SW5-WH</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -10840,7 +10837,7 @@
         </is>
       </c>
       <c r="K203" t="n">
-        <v>23.11</v>
+        <v>3.14</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -10848,17 +10845,17 @@
         </is>
       </c>
       <c r="M203" t="n">
-        <v>1132.39</v>
+        <v>474.14</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>KE-000041</t>
+          <t>KE-000040</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -10875,24 +10872,24 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>C00316</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>LED-PNL-60x60-40W</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>450</v>
+        <v>49</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K204" t="n">
-        <v>0.21</v>
+        <v>23.11</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -10900,7 +10897,7 @@
         </is>
       </c>
       <c r="M204" t="n">
-        <v>94.5</v>
+        <v>1132.39</v>
       </c>
     </row>
     <row r="205">
@@ -10910,7 +10907,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -10932,19 +10929,19 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>WD-ELG-SW7-AN</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>44</v>
+        <v>450</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K205" t="n">
-        <v>9.83</v>
+        <v>0.21</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -10952,7 +10949,7 @@
         </is>
       </c>
       <c r="M205" t="n">
-        <v>432.52</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="206">
@@ -10962,7 +10959,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -10984,11 +10981,11 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>WD-ELG-SOC2-WH</t>
+          <t>WD-ELG-SW7-AN</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -10996,7 +10993,7 @@
         </is>
       </c>
       <c r="K206" t="n">
-        <v>9.52</v>
+        <v>9.83</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -11004,17 +11001,17 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>95.2</v>
+        <v>432.52</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>KE-000042</t>
+          <t>KE-000041</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -11031,24 +11028,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C00101</t>
+          <t>C00316</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>WD-ELG-SOC2-WH</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K207" t="n">
-        <v>0.97</v>
+        <v>9.52</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -11056,7 +11053,7 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>252.2</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="208">
@@ -11066,7 +11063,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -11088,19 +11085,19 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>WD-NOV-FR1-IV</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K208" t="n">
-        <v>1.42</v>
+        <v>0.97</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -11108,7 +11105,7 @@
         </is>
       </c>
       <c r="M208" t="n">
-        <v>25.56</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="209">
@@ -11118,7 +11115,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -11140,11 +11137,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>WD-ELG-SW1-AN</t>
+          <t>WD-NOV-FR1-IV</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -11152,7 +11149,7 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>5.05</v>
+        <v>1.42</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -11160,7 +11157,7 @@
         </is>
       </c>
       <c r="M209" t="n">
-        <v>65.65000000000001</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="210">
@@ -11170,7 +11167,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -11192,11 +11189,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-ELG-SW1-AN</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -11204,7 +11201,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>5.71</v>
+        <v>5.05</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -11212,7 +11209,7 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>5.71</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -11222,7 +11219,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -11244,11 +11241,11 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>DB-36-SF</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -11256,7 +11253,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>35.39</v>
+        <v>5.71</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -11264,17 +11261,17 @@
         </is>
       </c>
       <c r="M211" t="n">
-        <v>176.95</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KE-000043</t>
+          <t>KE-000042</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -11291,16 +11288,16 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C00349</t>
+          <t>C00101</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>DB-36-SF</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -11308,7 +11305,7 @@
         </is>
       </c>
       <c r="K212" t="n">
-        <v>7.25</v>
+        <v>35.39</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -11316,7 +11313,7 @@
         </is>
       </c>
       <c r="M212" t="n">
-        <v>72.5</v>
+        <v>176.95</v>
       </c>
     </row>
     <row r="213">
@@ -11326,7 +11323,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -11348,11 +11345,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>CLP-CAB-9-12</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -11360,7 +11357,7 @@
         </is>
       </c>
       <c r="K213" t="n">
-        <v>0.06</v>
+        <v>7.25</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -11368,17 +11365,17 @@
         </is>
       </c>
       <c r="M213" t="n">
-        <v>4.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>KE-000044</t>
+          <t>KE-000043</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -11395,24 +11392,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C00222</t>
+          <t>C00349</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>CLP-CAB-9-12</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2660</v>
+        <v>75</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K214" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -11420,7 +11417,7 @@
         </is>
       </c>
       <c r="M214" t="n">
-        <v>532</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="215">
@@ -11430,7 +11427,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -11452,19 +11449,19 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>BRK-B40-1P</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I215" t="n">
-        <v>127</v>
+        <v>2660</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K215" t="n">
-        <v>5.08</v>
+        <v>0.2</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -11472,7 +11469,7 @@
         </is>
       </c>
       <c r="M215" t="n">
-        <v>645.16</v>
+        <v>532</v>
       </c>
     </row>
     <row r="216">
@@ -11482,7 +11479,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -11504,11 +11501,11 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>BRK-C25-3P</t>
+          <t>BRK-B40-1P</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -11516,7 +11513,7 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>18.15</v>
+        <v>5.08</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -11524,7 +11521,7 @@
         </is>
       </c>
       <c r="M216" t="n">
-        <v>1234.2</v>
+        <v>645.16</v>
       </c>
     </row>
     <row r="217">
@@ -11534,7 +11531,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -11556,11 +11553,11 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>BRK-C25-3P</t>
         </is>
       </c>
       <c r="I217" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -11568,7 +11565,7 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>5.39</v>
+        <v>18.15</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -11576,17 +11573,17 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>490.49</v>
+        <v>1234.2</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>KE-000045</t>
+          <t>KE-000044</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -11603,16 +11600,16 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>C00287</t>
+          <t>C00222</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>BRK-B16-1P</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -11620,7 +11617,7 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>5.04</v>
+        <v>5.39</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -11628,7 +11625,7 @@
         </is>
       </c>
       <c r="M218" t="n">
-        <v>100.8</v>
+        <v>490.49</v>
       </c>
     </row>
     <row r="219">
@@ -11638,7 +11635,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -11660,11 +11657,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>BRK-B32-1P</t>
+          <t>BRK-B16-1P</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -11672,7 +11669,7 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>5.89</v>
+        <v>5.04</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -11680,7 +11677,7 @@
         </is>
       </c>
       <c r="M219" t="n">
-        <v>88.34999999999999</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="220">
@@ -11690,7 +11687,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -11712,11 +11709,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>WD-ELG-SW1-AN</t>
+          <t>BRK-B32-1P</t>
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -11724,7 +11721,7 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>5.16</v>
+        <v>5.89</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -11732,7 +11729,7 @@
         </is>
       </c>
       <c r="M220" t="n">
-        <v>15.48</v>
+        <v>88.34999999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11742,7 +11739,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -11764,11 +11761,11 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>BOX-KO8</t>
+          <t>WD-ELG-SW1-AN</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -11776,7 +11773,7 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>0.8</v>
+        <v>5.16</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -11784,17 +11781,17 @@
         </is>
       </c>
       <c r="M221" t="n">
-        <v>20</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>KE-000046</t>
+          <t>KE-000045</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -11811,16 +11808,16 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C00400</t>
+          <t>C00287</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>BOX-KO8</t>
         </is>
       </c>
       <c r="I222" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -11828,7 +11825,7 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>6.99</v>
+        <v>0.8</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -11836,13 +11833,13 @@
         </is>
       </c>
       <c r="M222" t="n">
-        <v>125.82</v>
+        <v>20</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>KE-000047</t>
+          <t>KE-000046</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -11863,16 +11860,16 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C00287</t>
+          <t>C00400</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-IV</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -11880,7 +11877,7 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>4.79</v>
+        <v>6.99</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -11888,7 +11885,7 @@
         </is>
       </c>
       <c r="M223" t="n">
-        <v>38.32</v>
+        <v>125.82</v>
       </c>
     </row>
     <row r="224">
@@ -11898,7 +11895,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -11920,11 +11917,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW6-IV</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -11932,7 +11929,7 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>7.19</v>
+        <v>4.79</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -11940,7 +11937,7 @@
         </is>
       </c>
       <c r="M224" t="n">
-        <v>86.28</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="225">
@@ -11950,7 +11947,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -11972,11 +11969,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>WD-ELG-SW1-AN</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -11984,7 +11981,7 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>5.16</v>
+        <v>7.19</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -11992,7 +11989,7 @@
         </is>
       </c>
       <c r="M225" t="n">
-        <v>103.2</v>
+        <v>86.28</v>
       </c>
     </row>
     <row r="226">
@@ -12002,7 +11999,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -12024,11 +12021,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-ELG-SW1-AN</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -12036,7 +12033,7 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>5.83</v>
+        <v>5.16</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -12044,7 +12041,7 @@
         </is>
       </c>
       <c r="M226" t="n">
-        <v>52.47</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="227">
@@ -12054,7 +12051,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -12076,11 +12073,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>LED-FLD-20W</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -12088,7 +12085,7 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>11.09</v>
+        <v>5.83</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -12096,17 +12093,17 @@
         </is>
       </c>
       <c r="M227" t="n">
-        <v>44.36</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>KE-000048</t>
+          <t>KE-000047</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -12123,24 +12120,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C00191</t>
+          <t>C00287</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>CAB-CYA-4-BK</t>
+          <t>LED-FLD-20W</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K228" t="n">
-        <v>0.55</v>
+        <v>11.09</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -12148,7 +12145,7 @@
         </is>
       </c>
       <c r="M228" t="n">
-        <v>66</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="229">
@@ -12158,7 +12155,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -12180,19 +12177,19 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>CAB-CYA-4-BK</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K229" t="n">
-        <v>4</v>
+        <v>0.55</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -12200,7 +12197,7 @@
         </is>
       </c>
       <c r="M229" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="230">
@@ -12210,7 +12207,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -12232,11 +12229,11 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I230" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -12244,7 +12241,7 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -12252,17 +12249,17 @@
         </is>
       </c>
       <c r="M230" t="n">
-        <v>80.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>KE-000049</t>
+          <t>KE-000048</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -12270,7 +12267,7 @@
         </is>
       </c>
       <c r="E231" s="1" t="n">
-        <v>45936</v>
+        <v>45933</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -12279,24 +12276,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00191</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>CAB-CGSG-3x2.5</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>840</v>
+        <v>14</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K231" t="n">
-        <v>1.63</v>
+        <v>5.75</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -12304,7 +12301,7 @@
         </is>
       </c>
       <c r="M231" t="n">
-        <v>1369.2</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="232">
@@ -12314,7 +12311,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -12336,11 +12333,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>CAB-CYA-2.5-BN</t>
+          <t>CAB-CGSG-3x2.5</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>920</v>
+        <v>840</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -12348,7 +12345,7 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>0.35</v>
+        <v>1.63</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -12356,7 +12353,7 @@
         </is>
       </c>
       <c r="M232" t="n">
-        <v>322</v>
+        <v>1369.2</v>
       </c>
     </row>
     <row r="233">
@@ -12366,7 +12363,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -12388,11 +12385,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CYA-2.5-BN</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2330</v>
+        <v>920</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -12400,7 +12397,7 @@
         </is>
       </c>
       <c r="K233" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -12408,7 +12405,7 @@
         </is>
       </c>
       <c r="M233" t="n">
-        <v>2050.4</v>
+        <v>322</v>
       </c>
     </row>
     <row r="234">
@@ -12418,7 +12415,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -12440,19 +12437,16 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>BRK-C13-3P</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I234" t="n">
-        <v>78</v>
+        <v>2330</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="K234" t="n">
-        <v>16.07</v>
+          <t>m</t>
+        </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -12460,7 +12454,7 @@
         </is>
       </c>
       <c r="M234" t="n">
-        <v>1253.46</v>
+        <v>2050.4</v>
       </c>
     </row>
     <row r="235">
@@ -12470,7 +12464,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -12492,11 +12486,11 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>RCD-40-30-2P</t>
+          <t>BRK-C13-3P</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -12504,7 +12498,7 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>22.79</v>
+        <v>16.07</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -12512,7 +12506,7 @@
         </is>
       </c>
       <c r="M235" t="n">
-        <v>3600.82</v>
+        <v>1253.46</v>
       </c>
     </row>
     <row r="236">
@@ -12522,7 +12516,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -12544,11 +12538,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>WD-CLS-SW6-IV</t>
+          <t>RCD-40-30-2P</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -12556,7 +12550,7 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>3.06</v>
+        <v>22.79</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -12564,7 +12558,7 @@
         </is>
       </c>
       <c r="M236" t="n">
-        <v>180.54</v>
+        <v>3600.82</v>
       </c>
     </row>
     <row r="237">
@@ -12574,7 +12568,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -12596,11 +12590,11 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-WH</t>
+          <t>WD-CLS-SW6-IV</t>
         </is>
       </c>
       <c r="I237" t="n">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -12608,7 +12602,7 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>3.73</v>
+        <v>3.06</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -12616,7 +12610,7 @@
         </is>
       </c>
       <c r="M237" t="n">
-        <v>503.55</v>
+        <v>180.54</v>
       </c>
     </row>
     <row r="238">
@@ -12626,7 +12620,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -12648,11 +12642,11 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>WD-NOV-SW1-WH</t>
         </is>
       </c>
       <c r="I238" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -12660,7 +12654,7 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -12668,7 +12662,7 @@
         </is>
       </c>
       <c r="M238" t="n">
-        <v>129.96</v>
+        <v>503.55</v>
       </c>
     </row>
     <row r="239">
@@ -12678,7 +12672,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -12700,11 +12694,11 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-WH</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I239" t="n">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -12712,7 +12706,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>4.09</v>
+        <v>3.61</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -12720,7 +12714,7 @@
         </is>
       </c>
       <c r="M239" t="n">
-        <v>785.28</v>
+        <v>129.96</v>
       </c>
     </row>
     <row r="240">
@@ -12730,7 +12724,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -12752,11 +12746,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>WD-NOV-SOC2-WH</t>
+          <t>WD-NOV-SW6-WH</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -12764,7 +12758,7 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>5.97</v>
+        <v>4.09</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -12772,7 +12766,7 @@
         </is>
       </c>
       <c r="M240" t="n">
-        <v>1164.15</v>
+        <v>785.28</v>
       </c>
     </row>
     <row r="241">
@@ -12782,7 +12776,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -12804,11 +12798,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>WD-ELG-FR2-AN</t>
+          <t>WD-NOV-SOC2-WH</t>
         </is>
       </c>
       <c r="I241" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -12816,7 +12810,7 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>4.02</v>
+        <v>5.97</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -12824,7 +12818,7 @@
         </is>
       </c>
       <c r="M241" t="n">
-        <v>586.92</v>
+        <v>1164.15</v>
       </c>
     </row>
     <row r="242">
@@ -12834,7 +12828,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -12856,11 +12850,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>TRM-3X25</t>
+          <t>WD-ELG-FR2-AN</t>
         </is>
       </c>
       <c r="I242" t="n">
-        <v>925</v>
+        <v>146</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -12868,7 +12862,7 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>0.14</v>
+        <v>4.02</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -12876,17 +12870,17 @@
         </is>
       </c>
       <c r="M242" t="n">
-        <v>129.5</v>
+        <v>586.92</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>KE-000050</t>
+          <t>KE-000049</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -12903,16 +12897,16 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>C00133</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>TRM-3X25</t>
         </is>
       </c>
       <c r="I243" t="n">
-        <v>19</v>
+        <v>925</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -12920,7 +12914,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>5.55</v>
+        <v>0.14</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -12928,7 +12922,7 @@
         </is>
       </c>
       <c r="M243" t="n">
-        <v>105.45</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="244">
@@ -12938,7 +12932,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -12960,11 +12954,11 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -12972,7 +12966,7 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>6.94</v>
+        <v>5.55</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -12980,17 +12974,17 @@
         </is>
       </c>
       <c r="M244" t="n">
-        <v>20.82</v>
+        <v>105.45</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>KE-000051</t>
+          <t>KE-000050</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -13007,24 +13001,24 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00133</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2100</v>
+        <v>3</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K245" t="n">
-        <v>1.97</v>
+        <v>6.94</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -13032,7 +13026,7 @@
         </is>
       </c>
       <c r="M245" t="n">
-        <v>4137</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="246">
@@ -13042,7 +13036,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -13064,11 +13058,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>CAB-CYA-4-BN</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2360</v>
+        <v>2100</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -13076,7 +13070,7 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>0.5</v>
+        <v>1.97</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -13084,7 +13078,7 @@
         </is>
       </c>
       <c r="M246" t="n">
-        <v>1180</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="247">
@@ -13094,7 +13088,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -13116,11 +13110,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CYA-4-BN</t>
         </is>
       </c>
       <c r="I247" t="n">
-        <v>550</v>
+        <v>2360</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -13128,7 +13122,7 @@
         </is>
       </c>
       <c r="K247" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -13136,7 +13130,7 @@
         </is>
       </c>
       <c r="M247" t="n">
-        <v>484</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="248">
@@ -13146,7 +13140,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -13168,19 +13162,19 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>BRK-C10-3P</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I248" t="n">
-        <v>62</v>
+        <v>550</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K248" t="n">
-        <v>15.93</v>
+        <v>0.88</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -13188,7 +13182,7 @@
         </is>
       </c>
       <c r="M248" t="n">
-        <v>987.66</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249">
@@ -13198,7 +13192,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -13220,11 +13214,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>BRK-C10-3P</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -13232,7 +13226,7 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>3.61</v>
+        <v>15.93</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -13240,7 +13234,7 @@
         </is>
       </c>
       <c r="M249" t="n">
-        <v>227.43</v>
+        <v>987.66</v>
       </c>
     </row>
     <row r="250">
@@ -13250,7 +13244,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -13272,11 +13266,11 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I250" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -13284,7 +13278,7 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>6.39</v>
+        <v>3.61</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -13292,7 +13286,7 @@
         </is>
       </c>
       <c r="M250" t="n">
-        <v>185.31</v>
+        <v>227.43</v>
       </c>
     </row>
     <row r="251">
@@ -13302,7 +13296,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -13324,11 +13318,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>WD-ELG-FR2-WH</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -13336,7 +13330,7 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>3.38</v>
+        <v>6.39</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -13344,7 +13338,7 @@
         </is>
       </c>
       <c r="M251" t="n">
-        <v>388.7</v>
+        <v>185.31</v>
       </c>
     </row>
     <row r="252">
@@ -13354,7 +13348,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -13376,11 +13370,11 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-ELG-FR2-WH</t>
         </is>
       </c>
       <c r="I252" t="n">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -13388,7 +13382,7 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>5.18</v>
+        <v>3.38</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -13396,7 +13390,7 @@
         </is>
       </c>
       <c r="M252" t="n">
-        <v>1030.82</v>
+        <v>388.7</v>
       </c>
     </row>
     <row r="253">
@@ -13406,7 +13400,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -13428,11 +13422,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>BOX-KU68-HW</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>950</v>
+        <v>199</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -13440,7 +13434,7 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>0.39</v>
+        <v>5.18</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -13448,7 +13442,7 @@
         </is>
       </c>
       <c r="M253" t="n">
-        <v>370.5</v>
+        <v>1030.82</v>
       </c>
     </row>
     <row r="254">
@@ -13458,7 +13452,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -13480,11 +13474,11 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>TRM-5X25</t>
+          <t>BOX-KU68-HW</t>
         </is>
       </c>
       <c r="I254" t="n">
-        <v>350</v>
+        <v>950</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -13492,7 +13486,7 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -13500,7 +13494,7 @@
         </is>
       </c>
       <c r="M254" t="n">
-        <v>66.5</v>
+        <v>370.5</v>
       </c>
     </row>
     <row r="255">
@@ -13510,7 +13504,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -13532,11 +13526,11 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>CLP-CAB-5-8</t>
+          <t>TRM-5X25</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -13544,7 +13538,7 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -13552,17 +13546,17 @@
         </is>
       </c>
       <c r="M255" t="n">
-        <v>3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>KE-000052</t>
+          <t>KE-000051</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -13579,24 +13573,24 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>C00400</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>CLP-CAB-5-8</t>
         </is>
       </c>
       <c r="I256" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K256" t="n">
-        <v>2.16</v>
+        <v>0.03</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -13604,7 +13598,7 @@
         </is>
       </c>
       <c r="M256" t="n">
-        <v>561.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -13614,7 +13608,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -13636,19 +13630,19 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>LED-GU10-7W</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I257" t="n">
-        <v>6</v>
+        <v>260</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K257" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -13656,17 +13650,17 @@
         </is>
       </c>
       <c r="M257" t="n">
-        <v>11.34</v>
+        <v>561.6</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>KE-000053</t>
+          <t>KE-000052</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -13688,19 +13682,19 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>CAB-CGSG-3x2.5</t>
+          <t>LED-GU10-7W</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K258" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -13708,7 +13702,7 @@
         </is>
       </c>
       <c r="M258" t="n">
-        <v>340.1</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="259">
@@ -13718,7 +13712,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -13740,11 +13734,11 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CGSG-3x2.5</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -13752,7 +13746,7 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>0.97</v>
+        <v>1.79</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -13760,7 +13754,7 @@
         </is>
       </c>
       <c r="M259" t="n">
-        <v>174.6</v>
+        <v>340.1</v>
       </c>
     </row>
     <row r="260">
@@ -13770,7 +13764,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -13792,19 +13786,19 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>WD-NOV-SW5-WH</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I260" t="n">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K260" t="n">
-        <v>5.18</v>
+        <v>0.97</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -13812,17 +13806,17 @@
         </is>
       </c>
       <c r="M260" t="n">
-        <v>46.62</v>
+        <v>174.6</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>KE-000054</t>
+          <t>KE-000053</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -13839,24 +13833,24 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C00287</t>
+          <t>C00400</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>WD-NOV-SW5-WH</t>
         </is>
       </c>
       <c r="I261" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K261" t="n">
-        <v>2.22</v>
+        <v>5.18</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -13864,7 +13858,7 @@
         </is>
       </c>
       <c r="M261" t="n">
-        <v>199.8</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="262">
@@ -13874,7 +13868,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -13896,19 +13890,19 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>WD-CLS-FR2-AN</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K262" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -13916,7 +13910,7 @@
         </is>
       </c>
       <c r="M262" t="n">
-        <v>25.8</v>
+        <v>199.8</v>
       </c>
     </row>
     <row r="263">
@@ -13926,7 +13920,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -13948,11 +13942,11 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>WD-NOV-SW5-AN</t>
+          <t>WD-CLS-FR2-AN</t>
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -13960,7 +13954,7 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>5.12</v>
+        <v>2.15</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -13968,7 +13962,7 @@
         </is>
       </c>
       <c r="M263" t="n">
-        <v>15.36</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="264">
@@ -13978,7 +13972,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -14000,7 +13994,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>WD-ELG-SW5-IV</t>
+          <t>WD-NOV-SW5-AN</t>
         </is>
       </c>
       <c r="I264" t="n">
@@ -14012,7 +14006,7 @@
         </is>
       </c>
       <c r="K264" t="n">
-        <v>7.83</v>
+        <v>5.12</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -14020,17 +14014,17 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>23.49</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>KE-000055</t>
+          <t>KE-000054</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -14047,24 +14041,24 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>C00328</t>
+          <t>C00287</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>WD-ELG-SW5-IV</t>
         </is>
       </c>
       <c r="I265" t="n">
-        <v>210</v>
+        <v>3</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K265" t="n">
-        <v>2.15</v>
+        <v>7.83</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -14072,13 +14066,13 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>451.5</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>KE-000056</t>
+          <t>KE-000055</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -14099,24 +14093,24 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C00237</t>
+          <t>C00328</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I266" t="n">
-        <v>15</v>
+        <v>210</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K266" t="n">
-        <v>5.66</v>
+        <v>2.15</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -14124,7 +14118,7 @@
         </is>
       </c>
       <c r="M266" t="n">
-        <v>84.90000000000001</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="267">
@@ -14134,7 +14128,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -14156,11 +14150,11 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I267" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -14168,7 +14162,7 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>3.99</v>
+        <v>5.66</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -14176,17 +14170,17 @@
         </is>
       </c>
       <c r="M267" t="n">
-        <v>183.54</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>KE-000057</t>
+          <t>KE-000056</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -14203,24 +14197,24 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00237</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1900</v>
+        <v>46</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K268" t="n">
-        <v>1.97</v>
+        <v>3.99</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -14228,7 +14222,7 @@
         </is>
       </c>
       <c r="M268" t="n">
-        <v>3743</v>
+        <v>183.54</v>
       </c>
     </row>
     <row r="269">
@@ -14238,7 +14232,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -14260,11 +14254,11 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1050</v>
+        <v>1900</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -14272,7 +14266,7 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>0.2</v>
+        <v>1.97</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -14280,7 +14274,7 @@
         </is>
       </c>
       <c r="M269" t="n">
-        <v>210</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="270">
@@ -14290,7 +14284,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -14312,19 +14306,19 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>RCBO-B16-30</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I270" t="n">
-        <v>123</v>
+        <v>1050</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K270" t="n">
-        <v>25.35</v>
+        <v>0.2</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -14332,7 +14326,7 @@
         </is>
       </c>
       <c r="M270" t="n">
-        <v>3118.05</v>
+        <v>210</v>
       </c>
     </row>
     <row r="271">
@@ -14342,7 +14336,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -14364,11 +14358,11 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>WD-CLS-SW6-IV</t>
+          <t>RCBO-B16-30</t>
         </is>
       </c>
       <c r="I271" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -14376,7 +14370,7 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>3.06</v>
+        <v>25.35</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -14384,7 +14378,7 @@
         </is>
       </c>
       <c r="M271" t="n">
-        <v>327.42</v>
+        <v>3118.05</v>
       </c>
     </row>
     <row r="272">
@@ -14394,7 +14388,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -14416,11 +14410,11 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>WD-CLS-SW7-IV</t>
+          <t>WD-CLS-SW6-IV</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -14428,7 +14422,7 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>4.3</v>
+        <v>3.06</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -14436,7 +14430,7 @@
         </is>
       </c>
       <c r="M272" t="n">
-        <v>180.6</v>
+        <v>327.42</v>
       </c>
     </row>
     <row r="273">
@@ -14446,7 +14440,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -14468,11 +14462,11 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>WD-CLS-FR3-IV</t>
+          <t>WD-CLS-SW7-IV</t>
         </is>
       </c>
       <c r="I273" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -14480,7 +14474,7 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>2.52</v>
+        <v>4.3</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -14488,7 +14482,7 @@
         </is>
       </c>
       <c r="M273" t="n">
-        <v>110.88</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="274">
@@ -14498,7 +14492,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -14520,11 +14514,11 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-CLS-FR3-IV</t>
         </is>
       </c>
       <c r="I274" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -14532,7 +14526,7 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>6.39</v>
+        <v>2.52</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -14540,7 +14534,7 @@
         </is>
       </c>
       <c r="M274" t="n">
-        <v>274.77</v>
+        <v>110.88</v>
       </c>
     </row>
     <row r="275">
@@ -14550,7 +14544,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -14572,11 +14566,11 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>WD-NOV-FR2-IV</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -14584,7 +14578,7 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>2.24</v>
+        <v>6.39</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -14592,7 +14586,7 @@
         </is>
       </c>
       <c r="M275" t="n">
-        <v>152.32</v>
+        <v>274.77</v>
       </c>
     </row>
     <row r="276">
@@ -14602,7 +14596,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -14624,11 +14618,11 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>WD-NOV-FR3-WH</t>
+          <t>WD-NOV-FR2-IV</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -14636,7 +14630,7 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>3.83</v>
+        <v>2.24</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -14644,7 +14638,7 @@
         </is>
       </c>
       <c r="M276" t="n">
-        <v>122.56</v>
+        <v>152.32</v>
       </c>
     </row>
     <row r="277">
@@ -14654,7 +14648,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -14676,11 +14670,11 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>WD-ELG-SW6-IV</t>
+          <t>WD-NOV-FR3-WH</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -14688,7 +14682,7 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>6.09</v>
+        <v>3.83</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -14696,7 +14690,7 @@
         </is>
       </c>
       <c r="M277" t="n">
-        <v>688.17</v>
+        <v>122.56</v>
       </c>
     </row>
     <row r="278">
@@ -14706,7 +14700,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -14728,11 +14722,11 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>CLP-CAB-9-12</t>
+          <t>WD-ELG-SW6-IV</t>
         </is>
       </c>
       <c r="I278" t="n">
-        <v>425</v>
+        <v>113</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -14740,7 +14734,7 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>0.05</v>
+        <v>6.09</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -14748,7 +14742,7 @@
         </is>
       </c>
       <c r="M278" t="n">
-        <v>21.25</v>
+        <v>688.17</v>
       </c>
     </row>
     <row r="279">
@@ -14758,7 +14752,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -14780,11 +14774,11 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>LED-GU10-7W</t>
+          <t>CLP-CAB-9-12</t>
         </is>
       </c>
       <c r="I279" t="n">
-        <v>55</v>
+        <v>425</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -14792,7 +14786,7 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>1.73</v>
+        <v>0.05</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -14800,17 +14794,17 @@
         </is>
       </c>
       <c r="M279" t="n">
-        <v>95.15000000000001</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>KE-000058</t>
+          <t>KE-000057</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -14827,24 +14821,24 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C00218</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>LED-GU10-7W</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1950</v>
+        <v>55</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K280" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -14852,7 +14846,7 @@
         </is>
       </c>
       <c r="M280" t="n">
-        <v>3997.5</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -14862,7 +14856,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -14884,11 +14878,11 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>CAB-CYA-10-BU</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1860</v>
+        <v>1950</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -14896,7 +14890,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -14904,7 +14898,7 @@
         </is>
       </c>
       <c r="M281" t="n">
-        <v>2380.8</v>
+        <v>3997.5</v>
       </c>
     </row>
     <row r="282">
@@ -14914,7 +14908,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -14936,19 +14930,19 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>CAB-CYA-10-BU</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>30</v>
+        <v>1860</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K282" t="n">
-        <v>3.74</v>
+        <v>1.28</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -14956,7 +14950,7 @@
         </is>
       </c>
       <c r="M282" t="n">
-        <v>112.2</v>
+        <v>2380.8</v>
       </c>
     </row>
     <row r="283">
@@ -14966,7 +14960,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -14988,11 +14982,11 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>WD-NOV-SW5-AN</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I283" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -15000,7 +14994,7 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>4.73</v>
+        <v>3.74</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -15008,7 +15002,7 @@
         </is>
       </c>
       <c r="M283" t="n">
-        <v>368.94</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="284">
@@ -15018,7 +15012,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -15040,11 +15034,11 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-WH</t>
+          <t>WD-NOV-SW5-AN</t>
         </is>
       </c>
       <c r="I284" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -15052,7 +15046,7 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>4.25</v>
+        <v>4.73</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -15060,7 +15054,7 @@
         </is>
       </c>
       <c r="M284" t="n">
-        <v>454.75</v>
+        <v>368.94</v>
       </c>
     </row>
     <row r="285">
@@ -15070,7 +15064,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -15092,11 +15086,11 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>BOX-KU68-1</t>
+          <t>WD-NOV-SW6-WH</t>
         </is>
       </c>
       <c r="I285" t="n">
-        <v>600</v>
+        <v>107</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -15104,7 +15098,7 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>0.21</v>
+        <v>4.25</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -15112,7 +15106,7 @@
         </is>
       </c>
       <c r="M285" t="n">
-        <v>126</v>
+        <v>454.75</v>
       </c>
     </row>
     <row r="286">
@@ -15122,7 +15116,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -15144,11 +15138,11 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>CLP-CAB-9-12</t>
+          <t>BOX-KU68-1</t>
         </is>
       </c>
       <c r="I286" t="n">
-        <v>125</v>
+        <v>600</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -15156,7 +15150,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -15164,7 +15158,7 @@
         </is>
       </c>
       <c r="M286" t="n">
-        <v>6.25</v>
+        <v>126</v>
       </c>
     </row>
     <row r="287">
@@ -15174,7 +15168,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -15196,11 +15190,11 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>LED-GU10-7W</t>
+          <t>CLP-CAB-9-12</t>
         </is>
       </c>
       <c r="I287" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -15208,7 +15202,7 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>1.79</v>
+        <v>0.05</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -15216,17 +15210,17 @@
         </is>
       </c>
       <c r="M287" t="n">
-        <v>281.03</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>KE-000059</t>
+          <t>KE-000058</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -15243,24 +15237,24 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00218</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x1.5</t>
+          <t>LED-GU10-7W</t>
         </is>
       </c>
       <c r="I288" t="n">
-        <v>570</v>
+        <v>157</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K288" t="n">
-        <v>1.13</v>
+        <v>1.79</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -15268,7 +15262,7 @@
         </is>
       </c>
       <c r="M288" t="n">
-        <v>644.1</v>
+        <v>281.03</v>
       </c>
     </row>
     <row r="289">
@@ -15278,7 +15272,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -15300,11 +15294,11 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>CAB-CYKYJ-5x1.5</t>
         </is>
       </c>
       <c r="I289" t="n">
-        <v>1190</v>
+        <v>570</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -15312,7 +15306,7 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>0.2</v>
+        <v>1.13</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -15320,7 +15314,7 @@
         </is>
       </c>
       <c r="M289" t="n">
-        <v>238</v>
+        <v>644.1</v>
       </c>
     </row>
     <row r="290">
@@ -15330,7 +15324,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -15352,19 +15346,19 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>BRK-C40-1P</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I290" t="n">
-        <v>73</v>
+        <v>1190</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K290" t="n">
-        <v>5.09</v>
+        <v>0.2</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -15372,7 +15366,7 @@
         </is>
       </c>
       <c r="M290" t="n">
-        <v>371.57</v>
+        <v>238</v>
       </c>
     </row>
     <row r="291">
@@ -15382,7 +15376,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -15404,11 +15398,11 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>RCD-40-30-2P</t>
+          <t>BRK-C40-1P</t>
         </is>
       </c>
       <c r="I291" t="n">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -15416,7 +15410,7 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>22.79</v>
+        <v>5.09</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -15424,7 +15418,7 @@
         </is>
       </c>
       <c r="M291" t="n">
-        <v>3053.86</v>
+        <v>371.57</v>
       </c>
     </row>
     <row r="292">
@@ -15434,7 +15428,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -15456,11 +15450,11 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>RCD-40-30-2P</t>
         </is>
       </c>
       <c r="I292" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -15468,7 +15462,7 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>6.39</v>
+        <v>22.79</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -15476,7 +15470,7 @@
         </is>
       </c>
       <c r="M292" t="n">
-        <v>485.64</v>
+        <v>3053.86</v>
       </c>
     </row>
     <row r="293">
@@ -15486,7 +15480,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -15508,11 +15502,11 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>CLP-CAB-5-8</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I293" t="n">
-        <v>500</v>
+        <v>76</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -15520,7 +15514,7 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>0.03</v>
+        <v>6.39</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -15528,17 +15522,17 @@
         </is>
       </c>
       <c r="M293" t="n">
-        <v>15</v>
+        <v>485.64</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>KE-000060</t>
+          <t>KE-000059</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -15555,16 +15549,16 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>C00007</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>CLP-CAB-5-8</t>
         </is>
       </c>
       <c r="I294" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -15572,7 +15566,7 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>7.1</v>
+        <v>0.03</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -15580,7 +15574,7 @@
         </is>
       </c>
       <c r="M294" t="n">
-        <v>269.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="295">
@@ -15590,7 +15584,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -15612,11 +15606,11 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>WD-ELG-SW1-AN</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I295" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -15624,7 +15618,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -15632,17 +15626,17 @@
         </is>
       </c>
       <c r="M295" t="n">
-        <v>51</v>
+        <v>269.8</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>KE-000061</t>
+          <t>KE-000060</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -15659,24 +15653,24 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>C00154</t>
+          <t>C00007</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>wd-elg-sw1-an</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K296" t="n">
-        <v>2.24</v>
+        <v>5.1</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -15684,13 +15678,13 @@
         </is>
       </c>
       <c r="M296" t="n">
-        <v>134.4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>KE-000062</t>
+          <t>KE-000061</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -15711,24 +15705,24 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>C00013</t>
+          <t>C00154</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>WD-CLS-SW6-IV</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I297" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K297" t="n">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -15736,7 +15730,7 @@
         </is>
       </c>
       <c r="M297" t="n">
-        <v>40.8</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="298">
@@ -15746,7 +15740,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -15768,7 +15762,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>WD-CLS-SW7-IV</t>
+          <t>WD-CLS-SW6-IV</t>
         </is>
       </c>
       <c r="I298" t="n">
@@ -15780,7 +15774,7 @@
         </is>
       </c>
       <c r="K298" t="n">
-        <v>4.77</v>
+        <v>3.4</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -15788,7 +15782,7 @@
         </is>
       </c>
       <c r="M298" t="n">
-        <v>57.24</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="299">
@@ -15798,7 +15792,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -15820,11 +15814,11 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>WD-CLS-SW7-IV</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -15832,7 +15826,7 @@
         </is>
       </c>
       <c r="K299" t="n">
-        <v>4.01</v>
+        <v>4.77</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -15840,7 +15834,7 @@
         </is>
       </c>
       <c r="M299" t="n">
-        <v>140.35</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="300">
@@ -15850,7 +15844,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -15872,11 +15866,11 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>WD-NOV-FR3-WH</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I300" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -15884,7 +15878,7 @@
         </is>
       </c>
       <c r="K300" t="n">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -15892,7 +15886,7 @@
         </is>
       </c>
       <c r="M300" t="n">
-        <v>97.75</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="301">
@@ -15902,7 +15896,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -15924,11 +15918,11 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>LED-GU10-7W</t>
+          <t>WD-NOV-FR3-WH</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -15936,7 +15930,7 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>1.92</v>
+        <v>4.25</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -15944,17 +15938,17 @@
         </is>
       </c>
       <c r="M301" t="n">
-        <v>21.12</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KE-000063</t>
+          <t>KE-000062</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -15971,24 +15965,24 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>C00139</t>
+          <t>C00013</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-GNYE</t>
+          <t>LED-GU10-7W</t>
         </is>
       </c>
       <c r="I302" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K302" t="n">
-        <v>0.21</v>
+        <v>1.92</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -15996,7 +15990,7 @@
         </is>
       </c>
       <c r="M302" t="n">
-        <v>16.8</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="303">
@@ -16006,7 +16000,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -16028,19 +16022,19 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>CAB-CYA-1.5-GNYE</t>
         </is>
       </c>
       <c r="I303" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K303" t="n">
-        <v>5.58</v>
+        <v>0.21</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -16048,7 +16042,7 @@
         </is>
       </c>
       <c r="M303" t="n">
-        <v>111.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="304">
@@ -16058,7 +16052,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -16080,11 +16074,11 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>WD-NOV-SW5-AN</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I304" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -16092,7 +16086,7 @@
         </is>
       </c>
       <c r="K304" t="n">
-        <v>4.97</v>
+        <v>5.58</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -16100,7 +16094,7 @@
         </is>
       </c>
       <c r="M304" t="n">
-        <v>9.94</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="305">
@@ -16110,7 +16104,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -16132,11 +16126,11 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>LED-STRIP-5M</t>
+          <t>WD-NOV-SW5-AN</t>
         </is>
       </c>
       <c r="I305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -16144,7 +16138,7 @@
         </is>
       </c>
       <c r="K305" t="n">
-        <v>7.56</v>
+        <v>4.97</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -16152,17 +16146,17 @@
         </is>
       </c>
       <c r="M305" t="n">
-        <v>22.68</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>KE-000064</t>
+          <t>KE-000063</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -16179,16 +16173,16 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>C00277</t>
+          <t>C00139</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>BRK-C32-3P</t>
+          <t>LED-STRIP-5M</t>
         </is>
       </c>
       <c r="I306" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -16196,7 +16190,7 @@
         </is>
       </c>
       <c r="K306" t="n">
-        <v>20.01</v>
+        <v>7.56</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -16204,7 +16198,7 @@
         </is>
       </c>
       <c r="M306" t="n">
-        <v>920.46</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="307">
@@ -16214,7 +16208,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -16236,11 +16230,11 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>BRK-C40-1P</t>
+          <t>BRK-C32-3P</t>
         </is>
       </c>
       <c r="I307" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -16248,7 +16242,7 @@
         </is>
       </c>
       <c r="K307" t="n">
-        <v>5.67</v>
+        <v>20.01</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -16256,7 +16250,7 @@
         </is>
       </c>
       <c r="M307" t="n">
-        <v>272.16</v>
+        <v>920.46</v>
       </c>
     </row>
     <row r="308">
@@ -16266,7 +16260,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -16288,11 +16282,11 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>WD-CLS-SW5-WH</t>
+          <t>BRK-C40-1P</t>
         </is>
       </c>
       <c r="I308" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -16300,7 +16294,7 @@
         </is>
       </c>
       <c r="K308" t="n">
-        <v>3.5</v>
+        <v>5.67</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -16308,7 +16302,7 @@
         </is>
       </c>
       <c r="M308" t="n">
-        <v>45.5</v>
+        <v>272.16</v>
       </c>
     </row>
     <row r="309">
@@ -16318,7 +16312,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -16340,11 +16334,11 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>WD-CLS-SW5-WH</t>
         </is>
       </c>
       <c r="I309" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -16352,7 +16346,7 @@
         </is>
       </c>
       <c r="K309" t="n">
-        <v>5.69</v>
+        <v>3.5</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -16360,7 +16354,7 @@
         </is>
       </c>
       <c r="M309" t="n">
-        <v>91.04000000000001</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="310">
@@ -16370,7 +16364,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -16392,11 +16386,11 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>WD-CLS-FR1-IV</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I310" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -16404,7 +16398,7 @@
         </is>
       </c>
       <c r="K310" t="n">
-        <v>1.17</v>
+        <v>5.69</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -16412,7 +16406,7 @@
         </is>
       </c>
       <c r="M310" t="n">
-        <v>40.95</v>
+        <v>91.04000000000001</v>
       </c>
     </row>
     <row r="311">
@@ -16422,7 +16416,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -16444,11 +16438,11 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>WD-ELG-SW6-IV</t>
+          <t>WD-CLS-FR1-IV</t>
         </is>
       </c>
       <c r="I311" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -16456,7 +16450,7 @@
         </is>
       </c>
       <c r="K311" t="n">
-        <v>6.78</v>
+        <v>1.17</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -16464,17 +16458,17 @@
         </is>
       </c>
       <c r="M311" t="n">
-        <v>311.88</v>
+        <v>40.95</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>KE-000065</t>
+          <t>KE-000064</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -16491,16 +16485,16 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>C00275</t>
+          <t>C00277</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-ELG-SW6-IV</t>
         </is>
       </c>
       <c r="I312" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -16508,7 +16502,7 @@
         </is>
       </c>
       <c r="K312" t="n">
-        <v>6.99</v>
+        <v>6.78</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -16516,13 +16510,13 @@
         </is>
       </c>
       <c r="M312" t="n">
-        <v>27.96</v>
+        <v>311.88</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>KE-R00001</t>
+          <t>KE-000065</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -16530,12 +16524,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>KE-000006</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E313" s="1" t="n">
@@ -16548,16 +16537,16 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>C00161</t>
+          <t>C00275</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I313" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -16565,7 +16554,7 @@
         </is>
       </c>
       <c r="K313" t="n">
-        <v>5.61</v>
+        <v>6.99</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -16573,13 +16562,13 @@
         </is>
       </c>
       <c r="M313" t="n">
-        <v>-44.88</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>KE-000066</t>
+          <t>KE-R00001</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -16587,11 +16576,16 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>KE-000006</t>
         </is>
       </c>
       <c r="E314" s="1" t="n">
-        <v>45937</v>
+        <v>45936</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -16600,16 +16594,16 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>C00101</t>
+          <t>C00161</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-AN</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I314" t="n">
-        <v>10</v>
+        <v>-8</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -16617,7 +16611,7 @@
         </is>
       </c>
       <c r="K314" t="n">
-        <v>6.82</v>
+        <v>5.61</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -16625,13 +16619,13 @@
         </is>
       </c>
       <c r="M314" t="n">
-        <v>68.2</v>
+        <v>-44.88</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>KE-000067</t>
+          <t>KE-000066</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -16652,16 +16646,16 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>C00275</t>
+          <t>C00101</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>WD-NOV-SW7-AN</t>
         </is>
       </c>
       <c r="I315" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -16669,7 +16663,7 @@
         </is>
       </c>
       <c r="K315" t="n">
-        <v>5.59</v>
+        <v>6.82</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -16677,13 +16671,13 @@
         </is>
       </c>
       <c r="M315" t="n">
-        <v>106.21</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>KE-000068</t>
+          <t>KE-000067</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -16704,16 +16698,16 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>C00385</t>
+          <t>C00275</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-WH</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I316" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -16721,7 +16715,7 @@
         </is>
       </c>
       <c r="K316" t="n">
-        <v>4.54</v>
+        <v>5.59</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -16729,7 +16723,7 @@
         </is>
       </c>
       <c r="M316" t="n">
-        <v>90.8</v>
+        <v>106.21</v>
       </c>
     </row>
     <row r="317">
@@ -16739,7 +16733,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -16761,11 +16755,11 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-AN</t>
+          <t>WD-NOV-SW6-WH</t>
         </is>
       </c>
       <c r="I317" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -16773,7 +16767,7 @@
         </is>
       </c>
       <c r="K317" t="n">
-        <v>4.66</v>
+        <v>4.54</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -16781,17 +16775,17 @@
         </is>
       </c>
       <c r="M317" t="n">
-        <v>130.48</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KE-000069</t>
+          <t>KE-000068</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -16808,16 +16802,16 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>C00349</t>
+          <t>C00385</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>BOX-KU68-1</t>
+          <t>WD-NOV-SW6-AN</t>
         </is>
       </c>
       <c r="I318" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -16825,7 +16819,7 @@
         </is>
       </c>
       <c r="K318" t="n">
-        <v>0.23</v>
+        <v>4.66</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -16833,13 +16827,13 @@
         </is>
       </c>
       <c r="M318" t="n">
-        <v>17.25</v>
+        <v>130.48</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>KE-000070</t>
+          <t>KE-000069</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -16860,16 +16854,16 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>C00239</t>
+          <t>C00349</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-AN</t>
+          <t>BOX-KU68-1</t>
         </is>
       </c>
       <c r="I319" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -16877,7 +16871,7 @@
         </is>
       </c>
       <c r="K319" t="n">
-        <v>4.45</v>
+        <v>0.23</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -16885,7 +16879,7 @@
         </is>
       </c>
       <c r="M319" t="n">
-        <v>53.4</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="320">
@@ -16895,7 +16889,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -16917,11 +16911,11 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW6-AN</t>
         </is>
       </c>
       <c r="I320" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -16929,7 +16923,7 @@
         </is>
       </c>
       <c r="K320" t="n">
-        <v>6.76</v>
+        <v>4.45</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -16937,17 +16931,17 @@
         </is>
       </c>
       <c r="M320" t="n">
-        <v>128.44</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>KE-000071</t>
+          <t>KE-000070</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -16964,24 +16958,24 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00239</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I321" t="n">
-        <v>2890</v>
+        <v>19</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K321" t="n">
-        <v>1.97</v>
+        <v>6.76</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -16989,7 +16983,7 @@
         </is>
       </c>
       <c r="M321" t="n">
-        <v>5693.3</v>
+        <v>128.44</v>
       </c>
     </row>
     <row r="322">
@@ -16999,7 +16993,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -17021,11 +17015,11 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I322" t="n">
-        <v>2080</v>
+        <v>2890</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -17033,7 +17027,7 @@
         </is>
       </c>
       <c r="K322" t="n">
-        <v>0.2</v>
+        <v>1.97</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -17041,7 +17035,7 @@
         </is>
       </c>
       <c r="M322" t="n">
-        <v>416</v>
+        <v>5693.3</v>
       </c>
     </row>
     <row r="323">
@@ -17051,7 +17045,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -17073,11 +17067,11 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I323" t="n">
-        <v>2680</v>
+        <v>2080</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -17085,7 +17079,7 @@
         </is>
       </c>
       <c r="K323" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -17093,7 +17087,7 @@
         </is>
       </c>
       <c r="M323" t="n">
-        <v>2358.4</v>
+        <v>416</v>
       </c>
     </row>
     <row r="324">
@@ -17103,7 +17097,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -17125,19 +17119,19 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>BRK-C20-3P</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I324" t="n">
-        <v>147</v>
+        <v>2680</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K324" t="n">
-        <v>16.55</v>
+        <v>0.88</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -17145,7 +17139,7 @@
         </is>
       </c>
       <c r="M324" t="n">
-        <v>2432.85</v>
+        <v>2358.4</v>
       </c>
     </row>
     <row r="325">
@@ -17155,7 +17149,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -17177,11 +17171,11 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>WD-CLS-SW6-WH</t>
+          <t>BRK-C20-3P</t>
         </is>
       </c>
       <c r="I325" t="n">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -17189,7 +17183,7 @@
         </is>
       </c>
       <c r="K325" t="n">
-        <v>2.95</v>
+        <v>16.55</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -17197,7 +17191,7 @@
         </is>
       </c>
       <c r="M325" t="n">
-        <v>510.35</v>
+        <v>2432.85</v>
       </c>
     </row>
     <row r="326">
@@ -17207,7 +17201,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -17229,11 +17223,11 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>TL-DRILL-68</t>
+          <t>WD-CLS-SW6-WH</t>
         </is>
       </c>
       <c r="I326" t="n">
-        <v>5</v>
+        <v>173</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -17241,7 +17235,7 @@
         </is>
       </c>
       <c r="K326" t="n">
-        <v>17.42</v>
+        <v>2.95</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -17249,17 +17243,17 @@
         </is>
       </c>
       <c r="M326" t="n">
-        <v>87.09999999999999</v>
+        <v>510.35</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>KE-000072</t>
+          <t>KE-000071</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -17276,24 +17270,24 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>C00140</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>CAB-CYKYO-2x1.5</t>
+          <t>TL-DRILL-68</t>
         </is>
       </c>
       <c r="I327" t="n">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K327" t="n">
-        <v>0.59</v>
+        <v>17.42</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -17301,7 +17295,7 @@
         </is>
       </c>
       <c r="M327" t="n">
-        <v>171.1</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="328">
@@ -17311,7 +17305,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -17333,11 +17327,11 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>CAB-CYA-4-BK</t>
+          <t>CAB-CYKYO-2x1.5</t>
         </is>
       </c>
       <c r="I328" t="n">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -17345,7 +17339,7 @@
         </is>
       </c>
       <c r="K328" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -17353,7 +17347,7 @@
         </is>
       </c>
       <c r="M328" t="n">
-        <v>91.8</v>
+        <v>171.1</v>
       </c>
     </row>
     <row r="329">
@@ -17363,7 +17357,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -17385,19 +17379,19 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>WD-CLS-FR1-AN</t>
+          <t>CAB-CYA-4-BK</t>
         </is>
       </c>
       <c r="I329" t="n">
-        <v>9</v>
+        <v>170</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K329" t="n">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -17405,17 +17399,17 @@
         </is>
       </c>
       <c r="M329" t="n">
-        <v>9.539999999999999</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>KE-000073</t>
+          <t>KE-000072</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -17432,24 +17426,24 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00140</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-3x1.5</t>
+          <t>WD-CLS-FR1-AN</t>
         </is>
       </c>
       <c r="I330" t="n">
-        <v>2870</v>
+        <v>9</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K330" t="n">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -17457,7 +17451,7 @@
         </is>
       </c>
       <c r="M330" t="n">
-        <v>2037.7</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="331">
@@ -17467,7 +17461,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -17489,11 +17483,11 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>CAB-CYA-4-BN</t>
+          <t>CAB-CYKYJ-3x1.5</t>
         </is>
       </c>
       <c r="I331" t="n">
-        <v>1780</v>
+        <v>2870</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -17501,7 +17495,7 @@
         </is>
       </c>
       <c r="K331" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -17509,7 +17503,7 @@
         </is>
       </c>
       <c r="M331" t="n">
-        <v>890</v>
+        <v>2037.7</v>
       </c>
     </row>
     <row r="332">
@@ -17519,7 +17513,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -17541,11 +17535,11 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BK</t>
+          <t>CAB-CYA-4-BN</t>
         </is>
       </c>
       <c r="I332" t="n">
-        <v>2140</v>
+        <v>1780</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -17553,7 +17547,7 @@
         </is>
       </c>
       <c r="K332" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -17561,7 +17555,7 @@
         </is>
       </c>
       <c r="M332" t="n">
-        <v>1968.8</v>
+        <v>890</v>
       </c>
     </row>
     <row r="333">
@@ -17571,7 +17565,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -17593,19 +17587,19 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>RCD-40-30-2P</t>
+          <t>CAB-CYA-6-BK</t>
         </is>
       </c>
       <c r="I333" t="n">
-        <v>98</v>
+        <v>2140</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K333" t="n">
-        <v>22.79</v>
+        <v>0.92</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -17613,7 +17607,7 @@
         </is>
       </c>
       <c r="M333" t="n">
-        <v>2233.42</v>
+        <v>1968.8</v>
       </c>
     </row>
     <row r="334">
@@ -17623,7 +17617,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -17645,11 +17639,11 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>RCD-40-30-2P</t>
         </is>
       </c>
       <c r="I334" t="n">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -17657,7 +17651,7 @@
         </is>
       </c>
       <c r="K334" t="n">
-        <v>3.61</v>
+        <v>22.79</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -17665,7 +17659,7 @@
         </is>
       </c>
       <c r="M334" t="n">
-        <v>685.9</v>
+        <v>2233.42</v>
       </c>
     </row>
     <row r="335">
@@ -17675,7 +17669,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -17697,11 +17691,11 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I335" t="n">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -17709,7 +17703,7 @@
         </is>
       </c>
       <c r="K335" t="n">
-        <v>6.39</v>
+        <v>3.61</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -17717,7 +17711,7 @@
         </is>
       </c>
       <c r="M335" t="n">
-        <v>402.57</v>
+        <v>685.9</v>
       </c>
     </row>
     <row r="336">
@@ -17727,7 +17721,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -17749,11 +17743,11 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>WD-NOV-SOC2-WH</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I336" t="n">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -17761,7 +17755,7 @@
         </is>
       </c>
       <c r="K336" t="n">
-        <v>5.97</v>
+        <v>6.39</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -17769,7 +17763,7 @@
         </is>
       </c>
       <c r="M336" t="n">
-        <v>1068.63</v>
+        <v>402.57</v>
       </c>
     </row>
     <row r="337">
@@ -17779,7 +17773,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -17801,11 +17795,11 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>WD-ELG-FR1-IV</t>
+          <t>WD-NOV-SOC2-WH</t>
         </is>
       </c>
       <c r="I337" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -17813,7 +17807,7 @@
         </is>
       </c>
       <c r="K337" t="n">
-        <v>1.98</v>
+        <v>5.97</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -17821,7 +17815,7 @@
         </is>
       </c>
       <c r="M337" t="n">
-        <v>312.84</v>
+        <v>1068.63</v>
       </c>
     </row>
     <row r="338">
@@ -17831,7 +17825,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -17853,11 +17847,11 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-ELG-FR1-IV</t>
         </is>
       </c>
       <c r="I338" t="n">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
@@ -17865,7 +17859,7 @@
         </is>
       </c>
       <c r="K338" t="n">
-        <v>5.18</v>
+        <v>1.98</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -17873,7 +17867,7 @@
         </is>
       </c>
       <c r="M338" t="n">
-        <v>523.1799999999999</v>
+        <v>312.84</v>
       </c>
     </row>
     <row r="339">
@@ -17883,7 +17877,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -17905,11 +17899,11 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>DB-12-SF</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I339" t="n">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -17917,7 +17911,7 @@
         </is>
       </c>
       <c r="K339" t="n">
-        <v>17.9</v>
+        <v>5.18</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -17925,7 +17919,7 @@
         </is>
       </c>
       <c r="M339" t="n">
-        <v>537</v>
+        <v>523.1799999999999</v>
       </c>
     </row>
     <row r="340">
@@ -17935,7 +17929,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -17957,11 +17951,11 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>DB-36-SF</t>
+          <t>DB-12-SF</t>
         </is>
       </c>
       <c r="I340" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -17969,7 +17963,7 @@
         </is>
       </c>
       <c r="K340" t="n">
-        <v>32.12</v>
+        <v>17.9</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -17977,17 +17971,17 @@
         </is>
       </c>
       <c r="M340" t="n">
-        <v>738.76</v>
+        <v>537</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>KE-000074</t>
+          <t>KE-000073</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -18009,19 +18003,19 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>DB-36-SF</t>
         </is>
       </c>
       <c r="I341" t="n">
-        <v>1240</v>
+        <v>23</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K341" t="n">
-        <v>1.97</v>
+        <v>32.12</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -18029,7 +18023,7 @@
         </is>
       </c>
       <c r="M341" t="n">
-        <v>2442.8</v>
+        <v>738.76</v>
       </c>
     </row>
     <row r="342">
@@ -18039,7 +18033,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -18061,19 +18055,19 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>BRK-C32-1P</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I342" t="n">
-        <v>200</v>
+        <v>1240</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K342" t="n">
-        <v>4.35</v>
+        <v>1.97</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -18081,7 +18075,7 @@
         </is>
       </c>
       <c r="M342" t="n">
-        <v>870</v>
+        <v>2442.8</v>
       </c>
     </row>
     <row r="343">
@@ -18091,7 +18085,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -18113,11 +18107,11 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>BRK-C32-1P</t>
         </is>
       </c>
       <c r="I343" t="n">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -18125,7 +18119,7 @@
         </is>
       </c>
       <c r="K343" t="n">
-        <v>6.39</v>
+        <v>4.35</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -18133,17 +18127,17 @@
         </is>
       </c>
       <c r="M343" t="n">
-        <v>754.02</v>
+        <v>870</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>KE-000075</t>
+          <t>KE-000074</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -18160,16 +18154,16 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>C00207</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>WD-CLS-SW7-IV</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I344" t="n">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
@@ -18177,7 +18171,7 @@
         </is>
       </c>
       <c r="K344" t="n">
-        <v>4.78</v>
+        <v>6.39</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -18185,7 +18179,7 @@
         </is>
       </c>
       <c r="M344" t="n">
-        <v>57.36</v>
+        <v>754.02</v>
       </c>
     </row>
     <row r="345">
@@ -18195,7 +18189,7 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -18217,11 +18211,11 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>WD-CLS-SW7-IV</t>
         </is>
       </c>
       <c r="I345" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
@@ -18229,7 +18223,7 @@
         </is>
       </c>
       <c r="K345" t="n">
-        <v>4.01</v>
+        <v>4.78</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -18237,7 +18231,7 @@
         </is>
       </c>
       <c r="M345" t="n">
-        <v>44.11</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="346">
@@ -18247,7 +18241,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -18269,11 +18263,11 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I346" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -18281,7 +18275,7 @@
         </is>
       </c>
       <c r="K346" t="n">
-        <v>7.11</v>
+        <v>4.01</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -18289,7 +18283,7 @@
         </is>
       </c>
       <c r="M346" t="n">
-        <v>14.22</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="347">
@@ -18299,7 +18293,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -18321,11 +18315,11 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>TRM-5X25</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I347" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -18333,7 +18327,7 @@
         </is>
       </c>
       <c r="K347" t="n">
-        <v>0.21</v>
+        <v>7.11</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -18341,17 +18335,17 @@
         </is>
       </c>
       <c r="M347" t="n">
-        <v>10.5</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>KE-000076</t>
+          <t>KE-000075</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -18368,24 +18362,24 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>C00287</t>
+          <t>C00207</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BK</t>
+          <t>TRM-5X25</t>
         </is>
       </c>
       <c r="I348" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K348" t="n">
-        <v>1.03</v>
+        <v>0.21</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -18393,13 +18387,13 @@
         </is>
       </c>
       <c r="M348" t="n">
-        <v>113.3</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>KE-000077</t>
+          <t>KE-000076</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -18420,24 +18414,24 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>C00133</t>
+          <t>C00287</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>BRK-C6-1P</t>
+          <t>CAB-CYA-6-BK</t>
         </is>
       </c>
       <c r="I349" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K349" t="n">
-        <v>4.83</v>
+        <v>1.03</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -18445,7 +18439,7 @@
         </is>
       </c>
       <c r="M349" t="n">
-        <v>24.15</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="350">
@@ -18455,7 +18449,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -18477,11 +18471,11 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>BRK-C6-1P</t>
         </is>
       </c>
       <c r="I350" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
@@ -18489,7 +18483,7 @@
         </is>
       </c>
       <c r="K350" t="n">
-        <v>3.92</v>
+        <v>4.83</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -18497,17 +18491,17 @@
         </is>
       </c>
       <c r="M350" t="n">
-        <v>23.52</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>KE-000078</t>
+          <t>KE-000077</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -18524,24 +18518,24 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00133</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>CAB-CYA-10-BU</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I351" t="n">
-        <v>1590</v>
+        <v>6</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K351" t="n">
-        <v>1.23</v>
+        <v>3.92</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -18549,7 +18543,7 @@
         </is>
       </c>
       <c r="M351" t="n">
-        <v>1955.7</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="352">
@@ -18559,7 +18553,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -18581,19 +18575,19 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>RCD-40-30-2P</t>
+          <t>CAB-CYA-10-BU</t>
         </is>
       </c>
       <c r="I352" t="n">
-        <v>137</v>
+        <v>1590</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K352" t="n">
-        <v>22.79</v>
+        <v>1.23</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -18601,7 +18595,7 @@
         </is>
       </c>
       <c r="M352" t="n">
-        <v>3122.23</v>
+        <v>1955.7</v>
       </c>
     </row>
     <row r="353">
@@ -18611,7 +18605,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -18633,11 +18627,11 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>WD-NOV-SOC1-IV</t>
+          <t>RCD-40-30-2P</t>
         </is>
       </c>
       <c r="I353" t="n">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
@@ -18645,7 +18639,7 @@
         </is>
       </c>
       <c r="K353" t="n">
-        <v>3.44</v>
+        <v>22.79</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -18653,17 +18647,17 @@
         </is>
       </c>
       <c r="M353" t="n">
-        <v>182.32</v>
+        <v>3122.23</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>KE-000079</t>
+          <t>KE-000078</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -18680,16 +18674,16 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>C00013</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-WH</t>
+          <t>WD-NOV-SOC1-IV</t>
         </is>
       </c>
       <c r="I354" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -18697,7 +18691,7 @@
         </is>
       </c>
       <c r="K354" t="n">
-        <v>4.54</v>
+        <v>3.44</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -18705,7 +18699,7 @@
         </is>
       </c>
       <c r="M354" t="n">
-        <v>72.64</v>
+        <v>182.32</v>
       </c>
     </row>
     <row r="355">
@@ -18715,7 +18709,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -18737,11 +18731,11 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW6-WH</t>
         </is>
       </c>
       <c r="I355" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
@@ -18749,7 +18743,7 @@
         </is>
       </c>
       <c r="K355" t="n">
-        <v>7.09</v>
+        <v>4.54</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -18757,7 +18751,7 @@
         </is>
       </c>
       <c r="M355" t="n">
-        <v>191.43</v>
+        <v>72.64</v>
       </c>
     </row>
     <row r="356">
@@ -18767,7 +18761,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -18789,11 +18783,11 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>WD-ELG-SW1-AN</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I356" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
@@ -18801,7 +18795,7 @@
         </is>
       </c>
       <c r="K356" t="n">
-        <v>5.09</v>
+        <v>7.09</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -18809,7 +18803,7 @@
         </is>
       </c>
       <c r="M356" t="n">
-        <v>162.88</v>
+        <v>191.43</v>
       </c>
     </row>
     <row r="357">
@@ -18819,7 +18813,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -18841,11 +18835,11 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>BOX-KU68-1</t>
+          <t>WD-ELG-SW1-AN</t>
         </is>
       </c>
       <c r="I357" t="n">
-        <v>225</v>
+        <v>32</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>
@@ -18853,7 +18847,7 @@
         </is>
       </c>
       <c r="K357" t="n">
-        <v>0.23</v>
+        <v>5.09</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -18861,7 +18855,7 @@
         </is>
       </c>
       <c r="M357" t="n">
-        <v>51.75</v>
+        <v>162.88</v>
       </c>
     </row>
     <row r="358">
@@ -18871,7 +18865,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -18893,11 +18887,11 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>LED-PNL-30x30-24W</t>
+          <t>BOX-KU68-1</t>
         </is>
       </c>
       <c r="I358" t="n">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -18905,7 +18899,7 @@
         </is>
       </c>
       <c r="K358" t="n">
-        <v>19.39</v>
+        <v>0.23</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -18913,17 +18907,17 @@
         </is>
       </c>
       <c r="M358" t="n">
-        <v>775.6</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>KE-000080</t>
+          <t>KE-000079</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -18940,24 +18934,24 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>C00153</t>
+          <t>C00013</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>LED-PNL-30x30-24W</t>
         </is>
       </c>
       <c r="I359" t="n">
-        <v>1070</v>
+        <v>40</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K359" t="n">
-        <v>0.21</v>
+        <v>19.39</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -18965,7 +18959,7 @@
         </is>
       </c>
       <c r="M359" t="n">
-        <v>224.7</v>
+        <v>775.6</v>
       </c>
     </row>
     <row r="360">
@@ -18975,7 +18969,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -18997,19 +18991,19 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>WD-CLS-SW7-IV</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I360" t="n">
-        <v>151</v>
+        <v>1070</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K360" t="n">
-        <v>4.64</v>
+        <v>0.21</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -19017,7 +19011,7 @@
         </is>
       </c>
       <c r="M360" t="n">
-        <v>700.64</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="361">
@@ -19027,7 +19021,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -19049,11 +19043,11 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>WD-CLS-SW7-IV</t>
         </is>
       </c>
       <c r="I361" t="n">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -19061,7 +19055,7 @@
         </is>
       </c>
       <c r="K361" t="n">
-        <v>5.52</v>
+        <v>4.64</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -19069,17 +19063,17 @@
         </is>
       </c>
       <c r="M361" t="n">
-        <v>491.28</v>
+        <v>700.64</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>KE-000081</t>
+          <t>KE-000080</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -19096,24 +19090,24 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>C00085</t>
+          <t>C00153</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I362" t="n">
-        <v>340</v>
+        <v>89</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K362" t="n">
-        <v>0.21</v>
+        <v>5.52</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -19121,7 +19115,7 @@
         </is>
       </c>
       <c r="M362" t="n">
-        <v>71.40000000000001</v>
+        <v>491.28</v>
       </c>
     </row>
     <row r="363">
@@ -19131,7 +19125,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -19153,11 +19147,11 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I363" t="n">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -19165,7 +19159,7 @@
         </is>
       </c>
       <c r="K363" t="n">
-        <v>0.96</v>
+        <v>0.21</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -19173,17 +19167,17 @@
         </is>
       </c>
       <c r="M363" t="n">
-        <v>240</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>KE-000082</t>
+          <t>KE-000081</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -19200,24 +19194,24 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>C00316</t>
+          <t>C00085</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>WD-NOV-SOC2-AN</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I364" t="n">
-        <v>49</v>
+        <v>250</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K364" t="n">
-        <v>7.2</v>
+        <v>0.96</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -19225,7 +19219,7 @@
         </is>
       </c>
       <c r="M364" t="n">
-        <v>352.8</v>
+        <v>240</v>
       </c>
     </row>
     <row r="365">
@@ -19235,7 +19229,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -19257,11 +19251,11 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-SOC2-AN</t>
         </is>
       </c>
       <c r="I365" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -19269,7 +19263,7 @@
         </is>
       </c>
       <c r="K365" t="n">
-        <v>5.67</v>
+        <v>7.2</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -19277,7 +19271,7 @@
         </is>
       </c>
       <c r="M365" t="n">
-        <v>130.41</v>
+        <v>352.8</v>
       </c>
     </row>
     <row r="366">
@@ -19287,7 +19281,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -19309,11 +19303,11 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>LED-FLD-50W</t>
+          <t>WD-ELG-FR3-WH</t>
         </is>
       </c>
       <c r="I366" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -19321,7 +19315,7 @@
         </is>
       </c>
       <c r="K366" t="n">
-        <v>14.77</v>
+        <v>5.67</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -19329,17 +19323,17 @@
         </is>
       </c>
       <c r="M366" t="n">
-        <v>384.02</v>
+        <v>130.41</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>KE-000083</t>
+          <t>KE-000082</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -19356,24 +19350,24 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>C00254</t>
+          <t>C00316</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>CAB-CYKYJ-5x2.5</t>
+          <t>LED-FLD-50W</t>
         </is>
       </c>
       <c r="I367" t="n">
-        <v>2010</v>
+        <v>26</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K367" t="n">
-        <v>1.97</v>
+        <v>14.77</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -19381,7 +19375,7 @@
         </is>
       </c>
       <c r="M367" t="n">
-        <v>3959.7</v>
+        <v>384.02</v>
       </c>
     </row>
     <row r="368">
@@ -19391,7 +19385,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -19413,11 +19407,11 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CYKYJ-5x2.5</t>
         </is>
       </c>
       <c r="I368" t="n">
-        <v>1400</v>
+        <v>2010</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -19425,7 +19419,7 @@
         </is>
       </c>
       <c r="K368" t="n">
-        <v>0.88</v>
+        <v>1.97</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -19433,7 +19427,7 @@
         </is>
       </c>
       <c r="M368" t="n">
-        <v>1232</v>
+        <v>3959.7</v>
       </c>
     </row>
     <row r="369">
@@ -19443,7 +19437,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -19465,11 +19459,11 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>CAB-CYA-10-GNYE</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I369" t="n">
-        <v>1290</v>
+        <v>1400</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -19477,7 +19471,7 @@
         </is>
       </c>
       <c r="K369" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -19485,7 +19479,7 @@
         </is>
       </c>
       <c r="M369" t="n">
-        <v>1664.1</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="370">
@@ -19495,7 +19489,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -19517,19 +19511,19 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>BRK-C6-3P</t>
+          <t>CAB-CYA-10-GNYE</t>
         </is>
       </c>
       <c r="I370" t="n">
-        <v>86</v>
+        <v>1290</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K370" t="n">
-        <v>18.23</v>
+        <v>1.29</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -19537,7 +19531,7 @@
         </is>
       </c>
       <c r="M370" t="n">
-        <v>1567.78</v>
+        <v>1664.1</v>
       </c>
     </row>
     <row r="371">
@@ -19547,7 +19541,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -19569,11 +19563,11 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>WD-CLS-FR2-WH</t>
+          <t>BRK-C6-3P</t>
         </is>
       </c>
       <c r="I371" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -19581,7 +19575,7 @@
         </is>
       </c>
       <c r="K371" t="n">
-        <v>1.8</v>
+        <v>18.23</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -19589,7 +19583,7 @@
         </is>
       </c>
       <c r="M371" t="n">
-        <v>82.8</v>
+        <v>1567.78</v>
       </c>
     </row>
     <row r="372">
@@ -19599,7 +19593,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -19621,11 +19615,11 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>WD-CLS-FR2-WH</t>
         </is>
       </c>
       <c r="I372" t="n">
-        <v>171</v>
+        <v>46</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
@@ -19633,7 +19627,7 @@
         </is>
       </c>
       <c r="K372" t="n">
-        <v>3.61</v>
+        <v>1.8</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -19641,7 +19635,7 @@
         </is>
       </c>
       <c r="M372" t="n">
-        <v>617.3099999999999</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="373">
@@ -19651,7 +19645,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -19673,11 +19667,11 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-AN</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I373" t="n">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -19685,7 +19679,7 @@
         </is>
       </c>
       <c r="K373" t="n">
-        <v>4.2</v>
+        <v>3.61</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -19693,7 +19687,7 @@
         </is>
       </c>
       <c r="M373" t="n">
-        <v>583.8</v>
+        <v>617.3099999999999</v>
       </c>
     </row>
     <row r="374">
@@ -19703,7 +19697,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -19725,11 +19719,11 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>WD-ELG-SW5-IV</t>
+          <t>WD-NOV-SW6-AN</t>
         </is>
       </c>
       <c r="I374" t="n">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -19737,7 +19731,7 @@
         </is>
       </c>
       <c r="K374" t="n">
-        <v>6.96</v>
+        <v>4.2</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -19745,7 +19739,7 @@
         </is>
       </c>
       <c r="M374" t="n">
-        <v>1211.04</v>
+        <v>583.8</v>
       </c>
     </row>
     <row r="375">
@@ -19755,7 +19749,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -19777,11 +19771,11 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>WD-ELG-SW5-AN</t>
+          <t>WD-ELG-SW5-IV</t>
         </is>
       </c>
       <c r="I375" t="n">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
@@ -19789,7 +19783,7 @@
         </is>
       </c>
       <c r="K375" t="n">
-        <v>7.04</v>
+        <v>6.96</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -19797,17 +19791,17 @@
         </is>
       </c>
       <c r="M375" t="n">
-        <v>1386.88</v>
+        <v>1211.04</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>KE-000084</t>
+          <t>KE-000083</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -19829,19 +19823,19 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>CAB-CGSG-3x1.5</t>
+          <t>WD-ELG-SW5-AN</t>
         </is>
       </c>
       <c r="I376" t="n">
-        <v>2490</v>
+        <v>197</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="K376" t="n">
-        <v>1.08</v>
+        <v>7.04</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -19849,7 +19843,7 @@
         </is>
       </c>
       <c r="M376" t="n">
-        <v>2689.2</v>
+        <v>1386.88</v>
       </c>
     </row>
     <row r="377">
@@ -19859,7 +19853,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -19881,11 +19875,11 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>CAB-CYA-1.5-BU</t>
+          <t>CAB-CGSG-3x1.5</t>
         </is>
       </c>
       <c r="I377" t="n">
-        <v>1200</v>
+        <v>2490</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -19893,7 +19887,7 @@
         </is>
       </c>
       <c r="K377" t="n">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -19901,7 +19895,7 @@
         </is>
       </c>
       <c r="M377" t="n">
-        <v>240</v>
+        <v>2689.2</v>
       </c>
     </row>
     <row r="378">
@@ -19911,7 +19905,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -19933,11 +19927,11 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>CAB-CYA-6-BU</t>
+          <t>CAB-CYA-1.5-BU</t>
         </is>
       </c>
       <c r="I378" t="n">
-        <v>2700</v>
+        <v>1200</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -19945,7 +19939,7 @@
         </is>
       </c>
       <c r="K378" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -19953,7 +19947,7 @@
         </is>
       </c>
       <c r="M378" t="n">
-        <v>2376</v>
+        <v>240</v>
       </c>
     </row>
     <row r="379">
@@ -19963,7 +19957,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -19985,19 +19979,19 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>BRK-C6-3P</t>
+          <t>CAB-CYA-6-BU</t>
         </is>
       </c>
       <c r="I379" t="n">
-        <v>129</v>
+        <v>2700</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>m</t>
         </is>
       </c>
       <c r="K379" t="n">
-        <v>18.23</v>
+        <v>0.88</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -20005,7 +19999,7 @@
         </is>
       </c>
       <c r="M379" t="n">
-        <v>2351.67</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="380">
@@ -20015,7 +20009,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -20037,11 +20031,11 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>BRK-C20-1P</t>
+          <t>BRK-C6-3P</t>
         </is>
       </c>
       <c r="I380" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -20049,7 +20043,7 @@
         </is>
       </c>
       <c r="K380" t="n">
-        <v>4.49</v>
+        <v>18.23</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -20057,7 +20051,7 @@
         </is>
       </c>
       <c r="M380" t="n">
-        <v>561.25</v>
+        <v>2351.67</v>
       </c>
     </row>
     <row r="381">
@@ -20067,7 +20061,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -20089,11 +20083,11 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>BRK-C32-1P</t>
+          <t>BRK-C20-1P</t>
         </is>
       </c>
       <c r="I381" t="n">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -20101,7 +20095,7 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>4.35</v>
+        <v>4.49</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -20109,7 +20103,7 @@
         </is>
       </c>
       <c r="M381" t="n">
-        <v>378.45</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="382">
@@ -20119,7 +20113,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -20141,11 +20135,11 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>RCD-25-30-2P</t>
+          <t>BRK-C32-1P</t>
         </is>
       </c>
       <c r="I382" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -20153,7 +20147,7 @@
         </is>
       </c>
       <c r="K382" t="n">
-        <v>23.89</v>
+        <v>4.35</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -20161,7 +20155,7 @@
         </is>
       </c>
       <c r="M382" t="n">
-        <v>3464.05</v>
+        <v>378.45</v>
       </c>
     </row>
     <row r="383">
@@ -20171,7 +20165,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -20193,11 +20187,11 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC1-WH</t>
+          <t>RCD-25-30-2P</t>
         </is>
       </c>
       <c r="I383" t="n">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -20205,7 +20199,7 @@
         </is>
       </c>
       <c r="K383" t="n">
-        <v>2.82</v>
+        <v>23.89</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -20213,7 +20207,7 @@
         </is>
       </c>
       <c r="M383" t="n">
-        <v>203.04</v>
+        <v>3464.05</v>
       </c>
     </row>
     <row r="384">
@@ -20223,7 +20217,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -20245,11 +20239,11 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-CLS-SOC1-WH</t>
         </is>
       </c>
       <c r="I384" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
@@ -20257,7 +20251,7 @@
         </is>
       </c>
       <c r="K384" t="n">
-        <v>6.39</v>
+        <v>2.82</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -20265,7 +20259,7 @@
         </is>
       </c>
       <c r="M384" t="n">
-        <v>549.54</v>
+        <v>203.04</v>
       </c>
     </row>
     <row r="385">
@@ -20275,7 +20269,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -20290,18 +20284,13 @@
           <t>KE</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>C00254</t>
-        </is>
-      </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>WD-ELG-SW7-AN</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I385" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -20309,7 +20298,7 @@
         </is>
       </c>
       <c r="K385" t="n">
-        <v>8.98</v>
+        <v>6.39</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -20317,17 +20306,17 @@
         </is>
       </c>
       <c r="M385" t="n">
-        <v>565.74</v>
+        <v>549.54</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>KE-000085</t>
+          <t>KE-000084</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -20344,16 +20333,16 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>C00277</t>
+          <t>C00254</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>BRK-B40-1P</t>
+          <t>WD-ELG-SW7-AN</t>
         </is>
       </c>
       <c r="I386" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
@@ -20361,7 +20350,7 @@
         </is>
       </c>
       <c r="K386" t="n">
-        <v>5.44</v>
+        <v>8.98</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -20369,7 +20358,7 @@
         </is>
       </c>
       <c r="M386" t="n">
-        <v>174.08</v>
+        <v>565.74</v>
       </c>
     </row>
     <row r="387">
@@ -20379,7 +20368,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -20401,11 +20390,11 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>WD-CLS-SOC2-AN</t>
+          <t>BRK-B40-1P</t>
         </is>
       </c>
       <c r="I387" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
@@ -20413,7 +20402,7 @@
         </is>
       </c>
       <c r="K387" t="n">
-        <v>5.69</v>
+        <v>5.44</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -20421,7 +20410,7 @@
         </is>
       </c>
       <c r="M387" t="n">
-        <v>153.63</v>
+        <v>174.08</v>
       </c>
     </row>
     <row r="388">
@@ -20431,7 +20420,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -20453,11 +20442,11 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>WD-CLS-FR3-IV</t>
+          <t>WD-CLS-SOC2-AN</t>
         </is>
       </c>
       <c r="I388" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -20465,7 +20454,7 @@
         </is>
       </c>
       <c r="K388" t="n">
-        <v>2.8</v>
+        <v>5.69</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -20473,7 +20462,7 @@
         </is>
       </c>
       <c r="M388" t="n">
-        <v>106.4</v>
+        <v>153.63</v>
       </c>
     </row>
     <row r="389">
@@ -20483,7 +20472,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -20505,11 +20494,11 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-WH</t>
+          <t>WD-CLS-FR3-IV</t>
         </is>
       </c>
       <c r="I389" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="J389" t="inlineStr">
         <is>
@@ -20517,7 +20506,7 @@
         </is>
       </c>
       <c r="K389" t="n">
-        <v>4.56</v>
+        <v>2.8</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -20525,7 +20514,7 @@
         </is>
       </c>
       <c r="M389" t="n">
-        <v>45.6</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="390">
@@ -20535,7 +20524,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -20557,11 +20546,11 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-AN</t>
+          <t>WD-NOV-SW6-WH</t>
         </is>
       </c>
       <c r="I390" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
@@ -20569,7 +20558,7 @@
         </is>
       </c>
       <c r="K390" t="n">
-        <v>4.68</v>
+        <v>4.56</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -20577,7 +20566,7 @@
         </is>
       </c>
       <c r="M390" t="n">
-        <v>131.04</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="391">
@@ -20587,7 +20576,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -20609,11 +20598,11 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>WD-ELG-SW7-AN</t>
+          <t>WD-NOV-SW6-AN</t>
         </is>
       </c>
       <c r="I391" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
@@ -20621,7 +20610,7 @@
         </is>
       </c>
       <c r="K391" t="n">
-        <v>10.01</v>
+        <v>4.68</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -20629,17 +20618,17 @@
         </is>
       </c>
       <c r="M391" t="n">
-        <v>490.49</v>
+        <v>131.04</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>KE-000086</t>
+          <t>KE-000085</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -20656,16 +20645,16 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>C00021</t>
+          <t>C00277</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>WD-CLS-FR2-AN</t>
+          <t>WD-ELG-SW7-AN</t>
         </is>
       </c>
       <c r="I392" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
@@ -20673,7 +20662,7 @@
         </is>
       </c>
       <c r="K392" t="n">
-        <v>2.12</v>
+        <v>10.01</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -20681,7 +20670,7 @@
         </is>
       </c>
       <c r="M392" t="n">
-        <v>63.6</v>
+        <v>490.49</v>
       </c>
     </row>
     <row r="393">
@@ -20691,7 +20680,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -20713,11 +20702,11 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>WD-NOV-SW1-AN</t>
+          <t>WD-CLS-FR2-AN</t>
         </is>
       </c>
       <c r="I393" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -20725,7 +20714,7 @@
         </is>
       </c>
       <c r="K393" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -20733,7 +20722,7 @@
         </is>
       </c>
       <c r="M393" t="n">
-        <v>176</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="394">
@@ -20743,7 +20732,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -20765,11 +20754,11 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>WD-NOV-SW6-AN</t>
+          <t>WD-NOV-SW1-AN</t>
         </is>
       </c>
       <c r="I394" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
@@ -20777,7 +20766,7 @@
         </is>
       </c>
       <c r="K394" t="n">
-        <v>4.66</v>
+        <v>4</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -20785,7 +20774,7 @@
         </is>
       </c>
       <c r="M394" t="n">
-        <v>55.92</v>
+        <v>176</v>
       </c>
     </row>
     <row r="395">
@@ -20795,7 +20784,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -20817,11 +20806,11 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>WD-NOV-SW7-WH</t>
+          <t>WD-NOV-SW6-AN</t>
         </is>
       </c>
       <c r="I395" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J395" t="inlineStr">
         <is>
@@ -20829,7 +20818,7 @@
         </is>
       </c>
       <c r="K395" t="n">
-        <v>7.08</v>
+        <v>4.66</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -20837,7 +20826,7 @@
         </is>
       </c>
       <c r="M395" t="n">
-        <v>120.36</v>
+        <v>55.92</v>
       </c>
     </row>
     <row r="396">
@@ -20847,7 +20836,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -20869,11 +20858,11 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>WD-NOV-FR1-WH</t>
+          <t>WD-NOV-SW7-WH</t>
         </is>
       </c>
       <c r="I396" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -20881,7 +20870,7 @@
         </is>
       </c>
       <c r="K396" t="n">
-        <v>1.51</v>
+        <v>7.08</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -20889,7 +20878,7 @@
         </is>
       </c>
       <c r="M396" t="n">
-        <v>15.1</v>
+        <v>120.36</v>
       </c>
     </row>
     <row r="397">
@@ -20899,7 +20888,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -20921,11 +20910,11 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>WD-NOV-FR2-IV</t>
+          <t>WD-NOV-FR1-WH</t>
         </is>
       </c>
       <c r="I397" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
@@ -20933,7 +20922,7 @@
         </is>
       </c>
       <c r="K397" t="n">
-        <v>2.48</v>
+        <v>1.51</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -20941,17 +20930,17 @@
         </is>
       </c>
       <c r="M397" t="n">
-        <v>89.28</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>KE-000087</t>
+          <t>KE-000086</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -20968,16 +20957,16 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>C00275</t>
+          <t>C00021</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>WD-ELG-FR3-WH</t>
+          <t>WD-NOV-FR2-IV</t>
         </is>
       </c>
       <c r="I398" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
@@ -20985,7 +20974,7 @@
         </is>
       </c>
       <c r="K398" t="n">
-        <v>5.67</v>
+        <v>2.48</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -20993,13 +20982,13 @@
         </is>
       </c>
       <c r="M398" t="n">
-        <v>68.04000000000001</v>
+        <v>89.28</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>KE-R00002</t>
+          <t>KE-000087</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -21007,12 +20996,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>KE-000006</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E399" s="1" t="n">
@@ -21025,31 +21009,88 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
+          <t>C00275</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>WD-ELG-FR3-WH</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>12</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="K399" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M399" t="n">
+        <v>68.04000000000001</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>KE-R00002</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>1</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>KE-000006</t>
+        </is>
+      </c>
+      <c r="E400" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>KE</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
           <t>C00161</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
+      <c r="H400" t="inlineStr">
         <is>
           <t>TL-KNIFE</t>
         </is>
       </c>
-      <c r="I399" t="n">
+      <c r="I400" t="n">
         <v>-5</v>
       </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="K399" t="n">
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="K400" t="n">
         <v>15.49</v>
       </c>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="M399" t="n">
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M400" t="n">
         <v>-77.45</v>
       </c>
     </row>
